--- a/Result/profitability/7772.xlsx
+++ b/Result/profitability/7772.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM9"/>
+  <dimension ref="A1:AM10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1573,6 +1573,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7772</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>96</v>
+      </c>
+      <c r="D10" t="n">
+        <v>73</v>
+      </c>
+      <c r="E10" t="n">
+        <v>23</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-5.85%</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="N10" t="n">
+        <v>30.12875</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1.428571428571429</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-7.349999999999998</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0.2318611987381702</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0.07999999999999999</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-6.669999999999998</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>-0.2150225660863958</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
